--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E360"/>
+  <dimension ref="A1:E361"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6519,9 +6519,26 @@
         <v>2026-09-12T23:31:51.787+04:00</v>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C361" t="str">
+        <v>260913</v>
+      </c>
+      <c r="D361" t="str">
+        <v>4-0-7-9</v>
+      </c>
+      <c r="E361" t="str">
+        <v>2026-09-13T23:36:19.406+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E360"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E361"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E361"/>
+  <dimension ref="A1:E362"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6536,9 +6536,26 @@
         <v>2026-09-13T23:36:19.406+04:00</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C362" t="str">
+        <v>260914</v>
+      </c>
+      <c r="D362" t="str">
+        <v>5-0-8-8</v>
+      </c>
+      <c r="E362" t="str">
+        <v>2026-09-15T00:59:42.811+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E361"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E362"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E362"/>
+  <dimension ref="A1:E363"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6553,9 +6553,26 @@
         <v>2026-09-15T00:59:42.811+04:00</v>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="B363" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C363" t="str">
+        <v>260915</v>
+      </c>
+      <c r="D363" t="str">
+        <v>1-8-6-1</v>
+      </c>
+      <c r="E363" t="str">
+        <v>2026-09-16T00:20:04.429+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E362"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E363"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E363"/>
+  <dimension ref="A1:E364"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6570,9 +6570,26 @@
         <v>2026-09-16T00:20:04.429+04:00</v>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C364" t="str">
+        <v>260916</v>
+      </c>
+      <c r="D364" t="str">
+        <v>4-9-7-2</v>
+      </c>
+      <c r="E364" t="str">
+        <v>2026-09-17T00:18:48.176+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E363"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E364"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E364"/>
+  <dimension ref="A1:E365"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6587,9 +6587,26 @@
         <v>2026-09-17T00:18:48.176+04:00</v>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C365" t="str">
+        <v>260917</v>
+      </c>
+      <c r="D365" t="str">
+        <v>4-1-9-9</v>
+      </c>
+      <c r="E365" t="str">
+        <v>2026-09-18T00:27:08.057+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E364"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E365"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E365"/>
+  <dimension ref="A1:E366"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6604,9 +6604,26 @@
         <v>2026-09-18T00:27:08.057+04:00</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B366" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C366" t="str">
+        <v>260918</v>
+      </c>
+      <c r="D366" t="str">
+        <v>8-3-8-4</v>
+      </c>
+      <c r="E366" t="str">
+        <v>2026-09-18T23:49:44.105+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E365"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E366"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E366"/>
+  <dimension ref="A1:E367"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6621,9 +6621,26 @@
         <v>2026-09-18T23:49:44.105+04:00</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>2026-09-19</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C367" t="str">
+        <v>260919</v>
+      </c>
+      <c r="D367" t="str">
+        <v>6-9-7-5</v>
+      </c>
+      <c r="E367" t="str">
+        <v>2026-09-19T23:26:41.337+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E366"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E367"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E367"/>
+  <dimension ref="A1:E368"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6638,9 +6638,26 @@
         <v>2026-09-19T23:26:41.337+04:00</v>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>2026-09-20</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C368" t="str">
+        <v>260920</v>
+      </c>
+      <c r="D368" t="str">
+        <v>9-8-3-6</v>
+      </c>
+      <c r="E368" t="str">
+        <v>2026-09-20T23:35:46.677+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E367"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E368"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E368"/>
+  <dimension ref="A1:E369"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6655,9 +6655,26 @@
         <v>2026-09-20T23:35:46.677+04:00</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C369" t="str">
+        <v>260921</v>
+      </c>
+      <c r="D369" t="str">
+        <v>2-4-3-8</v>
+      </c>
+      <c r="E369" t="str">
+        <v>2026-09-22T01:09:44.664+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E368"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E369"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E369"/>
+  <dimension ref="A1:E370"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6672,9 +6672,26 @@
         <v>2026-09-22T01:09:44.664+04:00</v>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C370" t="str">
+        <v>260922</v>
+      </c>
+      <c r="D370" t="str">
+        <v>5-9-9-1</v>
+      </c>
+      <c r="E370" t="str">
+        <v>2026-09-23T00:19:07.778+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E369"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E370"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E370"/>
+  <dimension ref="A1:E371"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6689,9 +6689,26 @@
         <v>2026-09-23T00:19:07.778+04:00</v>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C371" t="str">
+        <v>260923</v>
+      </c>
+      <c r="D371" t="str">
+        <v>3-4-5-8</v>
+      </c>
+      <c r="E371" t="str">
+        <v>2026-09-24T00:34:37.698+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E370"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E371"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E371"/>
+  <dimension ref="A1:E372"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6706,9 +6706,26 @@
         <v>2026-09-24T00:34:37.698+04:00</v>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C372" t="str">
+        <v>260924</v>
+      </c>
+      <c r="D372" t="str">
+        <v>9-0-7-1</v>
+      </c>
+      <c r="E372" t="str">
+        <v>2026-09-25T00:37:26.616+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E371"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E372"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E372"/>
+  <dimension ref="A1:E373"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6723,9 +6723,26 @@
         <v>2026-09-25T00:37:26.616+04:00</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>2026-09-25</v>
+      </c>
+      <c r="B373" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C373" t="str">
+        <v>260925</v>
+      </c>
+      <c r="D373" t="str">
+        <v>1-3-6-4</v>
+      </c>
+      <c r="E373" t="str">
+        <v>2026-09-26T00:36:42.748+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E372"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E373"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E373"/>
+  <dimension ref="A1:E374"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6740,9 +6740,26 @@
         <v>2026-09-26T00:36:42.748+04:00</v>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C374" t="str">
+        <v>260926</v>
+      </c>
+      <c r="D374" t="str">
+        <v>6-2-6-0</v>
+      </c>
+      <c r="E374" t="str">
+        <v>2026-09-27T00:01:42.123+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E373"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E374"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E374"/>
+  <dimension ref="A1:E375"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6757,9 +6757,26 @@
         <v>2026-09-27T00:01:42.123+04:00</v>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C375" t="str">
+        <v>260927</v>
+      </c>
+      <c r="D375" t="str">
+        <v>4-1-3-7</v>
+      </c>
+      <c r="E375" t="str">
+        <v>2026-09-28T00:16:09.998+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E374"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E375"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E375"/>
+  <dimension ref="A1:E376"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6774,9 +6774,26 @@
         <v>2026-09-28T00:16:09.998+04:00</v>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C376" t="str">
+        <v>260928</v>
+      </c>
+      <c r="D376" t="str">
+        <v>4-3-1-3</v>
+      </c>
+      <c r="E376" t="str">
+        <v>2026-09-29T02:35:41.506+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E375"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E376"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E376"/>
+  <dimension ref="A1:E377"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6791,9 +6791,26 @@
         <v>2026-09-29T02:35:41.506+04:00</v>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C377" t="str">
+        <v>260929</v>
+      </c>
+      <c r="D377" t="str">
+        <v>4-5-8-4</v>
+      </c>
+      <c r="E377" t="str">
+        <v>2026-09-30T01:28:41.698+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E376"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E377"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E377"/>
+  <dimension ref="A1:E378"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6808,9 +6808,26 @@
         <v>2026-09-30T01:28:41.698+04:00</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C378" t="str">
+        <v>260930</v>
+      </c>
+      <c r="D378" t="str">
+        <v>0-2-2-1</v>
+      </c>
+      <c r="E378" t="str">
+        <v>2026-10-01T01:28:57.703+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E377"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E378"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E378"/>
+  <dimension ref="A1:E379"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6825,9 +6825,26 @@
         <v>2026-10-01T01:28:57.703+04:00</v>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C379" t="str">
+        <v>261001</v>
+      </c>
+      <c r="D379" t="str">
+        <v>6-7-4-0</v>
+      </c>
+      <c r="E379" t="str">
+        <v>2026-10-02T01:53:48.799+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E378"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E379"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E379"/>
+  <dimension ref="A1:E380"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6842,9 +6842,26 @@
         <v>2026-10-02T01:53:48.799+04:00</v>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C380" t="str">
+        <v>261002</v>
+      </c>
+      <c r="D380" t="str">
+        <v>7-7-4-4</v>
+      </c>
+      <c r="E380" t="str">
+        <v>2026-10-03T01:23:31.412+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E379"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E380"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E380"/>
+  <dimension ref="A1:E381"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6859,9 +6859,26 @@
         <v>2026-10-03T01:23:31.412+04:00</v>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="B381" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C381" t="str">
+        <v>261003</v>
+      </c>
+      <c r="D381" t="str">
+        <v>6-3-6-0</v>
+      </c>
+      <c r="E381" t="str">
+        <v>2026-10-04T00:01:58.314+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E380"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E381"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E381"/>
+  <dimension ref="A1:E382"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6876,9 +6876,26 @@
         <v>2026-10-04T00:01:58.314+04:00</v>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C382" t="str">
+        <v>261004</v>
+      </c>
+      <c r="D382" t="str">
+        <v>7-2-8-4</v>
+      </c>
+      <c r="E382" t="str">
+        <v>2026-10-05T00:17:56.912+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E381"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E382"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E382"/>
+  <dimension ref="A1:E383"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6893,9 +6893,26 @@
         <v>2026-10-05T00:17:56.912+04:00</v>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C383" t="str">
+        <v>261005</v>
+      </c>
+      <c r="D383" t="str">
+        <v>8-5-9-0</v>
+      </c>
+      <c r="E383" t="str">
+        <v>2026-10-06T03:14:46.992+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E382"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E383"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E383"/>
+  <dimension ref="A1:E384"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6910,9 +6910,26 @@
         <v>2026-10-06T03:14:46.992+04:00</v>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C384" t="str">
+        <v>261006</v>
+      </c>
+      <c r="D384" t="str">
+        <v>6-6-9-9</v>
+      </c>
+      <c r="E384" t="str">
+        <v>2026-10-07T01:46:25.241+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E383"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E384"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E384"/>
+  <dimension ref="A1:E385"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6927,9 +6927,26 @@
         <v>2026-10-07T01:46:25.241+04:00</v>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C385" t="str">
+        <v>261007</v>
+      </c>
+      <c r="D385" t="str">
+        <v>8-5-8-5</v>
+      </c>
+      <c r="E385" t="str">
+        <v>2026-10-08T02:09:06.222+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E384"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E385"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E385"/>
+  <dimension ref="A1:E386"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6944,9 +6944,26 @@
         <v>2026-10-08T02:09:06.222+04:00</v>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>2026-10-08</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C386" t="str">
+        <v>261008</v>
+      </c>
+      <c r="D386" t="str">
+        <v>5-2-4-5</v>
+      </c>
+      <c r="E386" t="str">
+        <v>2026-10-09T02:15:23.031+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E385"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E386"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E386"/>
+  <dimension ref="A1:E387"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6961,9 +6961,26 @@
         <v>2026-10-09T02:15:23.031+04:00</v>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>2026-10-09</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C387" t="str">
+        <v>261009</v>
+      </c>
+      <c r="D387" t="str">
+        <v>4-6-6-9</v>
+      </c>
+      <c r="E387" t="str">
+        <v>2026-10-10T01:48:21.404+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E386"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E387"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E387"/>
+  <dimension ref="A1:E388"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6978,9 +6978,26 @@
         <v>2026-10-10T01:48:21.404+04:00</v>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>2026-10-10</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C388" t="str">
+        <v>261010</v>
+      </c>
+      <c r="D388" t="str">
+        <v>0-2-7-3</v>
+      </c>
+      <c r="E388" t="str">
+        <v>2026-10-11T00:37:16.721+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E387"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E388"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E388"/>
+  <dimension ref="A1:E389"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6995,9 +6995,26 @@
         <v>2026-10-11T00:37:16.721+04:00</v>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>2026-10-11</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C389" t="str">
+        <v>261011</v>
+      </c>
+      <c r="D389" t="str">
+        <v>8-8-3-4</v>
+      </c>
+      <c r="E389" t="str">
+        <v>2026-10-12T01:01:10.465+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E388"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E389"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E389"/>
+  <dimension ref="A1:E390"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7012,9 +7012,26 @@
         <v>2026-10-12T01:01:10.465+04:00</v>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C390" t="str">
+        <v>261012</v>
+      </c>
+      <c r="D390" t="str">
+        <v>5-6-3-5</v>
+      </c>
+      <c r="E390" t="str">
+        <v>2026-10-13T03:41:57.443+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E389"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E390"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E390"/>
+  <dimension ref="A1:E391"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7029,9 +7029,26 @@
         <v>2026-10-13T03:41:57.443+04:00</v>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C391" t="str">
+        <v>261013</v>
+      </c>
+      <c r="D391" t="str">
+        <v>8-0-6-8</v>
+      </c>
+      <c r="E391" t="str">
+        <v>2026-10-14T01:54:40.420+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E390"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E391"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E391"/>
+  <dimension ref="A1:E392"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7046,9 +7046,26 @@
         <v>2026-10-14T01:54:40.420+04:00</v>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C392" t="str">
+        <v>261014</v>
+      </c>
+      <c r="D392" t="str">
+        <v>6-3-8-8</v>
+      </c>
+      <c r="E392" t="str">
+        <v>2026-10-15T00:50:42.587+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E391"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E392"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E392"/>
+  <dimension ref="A1:E393"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7063,9 +7063,26 @@
         <v>2026-10-15T00:50:42.587+04:00</v>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C393" t="str">
+        <v>261015</v>
+      </c>
+      <c r="D393" t="str">
+        <v>0-9-2-3</v>
+      </c>
+      <c r="E393" t="str">
+        <v>2026-10-16T00:26:15.444+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E392"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E393"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E394"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7080,9 +7080,26 @@
         <v>2026-10-16T00:26:15.444+04:00</v>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C394" t="str">
+        <v>261016</v>
+      </c>
+      <c r="D394" t="str">
+        <v>8-2-4-5</v>
+      </c>
+      <c r="E394" t="str">
+        <v>2026-10-17T00:00:00.847+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E393"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E394"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E394"/>
+  <dimension ref="A1:E395"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7097,9 +7097,26 @@
         <v>2026-10-17T00:00:00.847+04:00</v>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C395" t="str">
+        <v>261017</v>
+      </c>
+      <c r="D395" t="str">
+        <v>4-8-8-5</v>
+      </c>
+      <c r="E395" t="str">
+        <v>2026-10-17T23:35:36.907+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E394"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E395"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E395"/>
+  <dimension ref="A1:E396"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7114,9 +7114,26 @@
         <v>2026-10-17T23:35:36.907+04:00</v>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>2026-10-18</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C396" t="str">
+        <v>261018</v>
+      </c>
+      <c r="D396" t="str">
+        <v>2-4-6-7</v>
+      </c>
+      <c r="E396" t="str">
+        <v>2026-10-18T23:30:40.507+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E395"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E396"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E396"/>
+  <dimension ref="A1:E397"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7131,9 +7131,26 @@
         <v>2026-10-18T23:30:40.507+04:00</v>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C397" t="str">
+        <v>261019</v>
+      </c>
+      <c r="D397" t="str">
+        <v>9-1-6-7</v>
+      </c>
+      <c r="E397" t="str">
+        <v>2026-10-20T01:38:23.890+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E396"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E397"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E397"/>
+  <dimension ref="A1:E398"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7148,9 +7148,26 @@
         <v>2026-10-20T01:38:23.890+04:00</v>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>2026-10-20</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C398" t="str">
+        <v>261020</v>
+      </c>
+      <c r="D398" t="str">
+        <v>4-6-6-8</v>
+      </c>
+      <c r="E398" t="str">
+        <v>2026-10-21T00:45:45.723+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E397"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E398"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E399"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7165,9 +7165,26 @@
         <v>2026-10-21T00:45:45.723+04:00</v>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C399" t="str">
+        <v>261021</v>
+      </c>
+      <c r="D399" t="str">
+        <v>9-3-2-4</v>
+      </c>
+      <c r="E399" t="str">
+        <v>2026-10-22T00:45:58.641+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E398"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E399"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E400"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7182,9 +7182,26 @@
         <v>2026-10-22T00:45:58.641+04:00</v>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C400" t="str">
+        <v>261022</v>
+      </c>
+      <c r="D400" t="str">
+        <v>4-8-4-5</v>
+      </c>
+      <c r="E400" t="str">
+        <v>2026-10-23T00:40:48.498+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E399"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E400"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:E401"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7199,9 +7199,26 @@
         <v>2026-10-23T00:40:48.498+04:00</v>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C401" t="str">
+        <v>261023</v>
+      </c>
+      <c r="D401" t="str">
+        <v>7-5-6-9</v>
+      </c>
+      <c r="E401" t="str">
+        <v>2026-10-24T00:32:52.566+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E400"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E401"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:E402"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7216,9 +7216,26 @@
         <v>2026-10-24T00:32:52.566+04:00</v>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="B402" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C402" t="str">
+        <v>261024</v>
+      </c>
+      <c r="D402" t="str">
+        <v>3-1-2-8</v>
+      </c>
+      <c r="E402" t="str">
+        <v>2026-10-24T23:37:19.411+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E401"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E402"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E402"/>
+  <dimension ref="A1:E403"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7233,9 +7233,26 @@
         <v>2026-10-24T23:37:19.411+04:00</v>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="B403" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C403" t="str">
+        <v>261025</v>
+      </c>
+      <c r="D403" t="str">
+        <v>3-3-2-7</v>
+      </c>
+      <c r="E403" t="str">
+        <v>2026-10-25T23:49:16.293+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E402"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E403"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E403"/>
+  <dimension ref="A1:E404"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7250,9 +7250,26 @@
         <v>2026-10-25T23:49:16.293+04:00</v>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="B404" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C404" t="str">
+        <v>261026</v>
+      </c>
+      <c r="D404" t="str">
+        <v>3-1-0-1</v>
+      </c>
+      <c r="E404" t="str">
+        <v>2026-10-27T01:43:45.095+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E403"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E404"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E404"/>
+  <dimension ref="A1:E405"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7267,9 +7267,26 @@
         <v>2026-10-27T01:43:45.095+04:00</v>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="B405" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C405" t="str">
+        <v>261027</v>
+      </c>
+      <c r="D405" t="str">
+        <v>3-8-6-8</v>
+      </c>
+      <c r="E405" t="str">
+        <v>2026-10-28T01:24:59.448+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E404"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E405"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E405"/>
+  <dimension ref="A1:E406"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7284,9 +7284,26 @@
         <v>2026-10-28T01:24:59.448+04:00</v>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="B406" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C406" t="str">
+        <v>261028</v>
+      </c>
+      <c r="D406" t="str">
+        <v>8-1-9-9</v>
+      </c>
+      <c r="E406" t="str">
+        <v>2026-10-29T01:47:35.133+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E405"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E406"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E406"/>
+  <dimension ref="A1:E407"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7301,9 +7301,26 @@
         <v>2026-10-29T01:47:35.133+04:00</v>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="B407" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C407" t="str">
+        <v>261029</v>
+      </c>
+      <c r="D407" t="str">
+        <v>6-2-7-6</v>
+      </c>
+      <c r="E407" t="str">
+        <v>2026-10-30T01:54:44.858+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E406"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E407"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/results_pick4.xlsx
+++ b/results_pick4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E407"/>
+  <dimension ref="A1:E408"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7318,9 +7318,26 @@
         <v>2026-10-30T01:54:44.858+04:00</v>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="B408" t="str">
+        <v>Pick 4</v>
+      </c>
+      <c r="C408" t="str">
+        <v>261030</v>
+      </c>
+      <c r="D408" t="str">
+        <v>8-2-6-6</v>
+      </c>
+      <c r="E408" t="str">
+        <v>2026-10-31T01:38:23.440+04:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E407"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E408"/>
   </ignoredErrors>
 </worksheet>
 </file>